--- a/output/pdf_financials_xlsx/TWO.xlsx
+++ b/output/pdf_financials_xlsx/TWO.xlsx
@@ -5700,43 +5700,43 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.255251</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.270506</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.433036</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.441854</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.477619</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.477619</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.477619</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.477619</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.834209</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.936409</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.027227</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.027227</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.504727</v>
       </c>
     </row>
     <row r="93">
@@ -7106,19 +7106,19 @@
         <v>0</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.509197</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.53624</v>
+        <v>0.228088</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.944003</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.71796</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-1.816654</v>
       </c>
     </row>
     <row r="119">
@@ -9344,7 +9344,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10778,7 +10782,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11452,7 +11460,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -15256,7 +15268,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -20716,7 +20732,11 @@
           <t>Exploration and evaluation assets expenditures, net</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -21382,7 +21402,11 @@
           <t>Exploration and evaluation assets expenditures, net</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -21942,7 +21966,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -22318,7 +22346,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TWO.xlsx
+++ b/output/pdf_financials_xlsx/TWO.xlsx
@@ -999,52 +999,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000826</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.02771</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.008163999999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000402</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00092</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000128</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000124</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.00018</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000183</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000331</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.009993</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.013956</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.060496</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.04598</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.084144</v>
       </c>
     </row>
     <row r="13">
@@ -1984,52 +1984,52 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.110692</v>
+        <v>-0.111518</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.991412</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.113998</v>
+        <v>-2.141708</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.319979</v>
+        <v>-3.328143</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.182222</v>
+        <v>-0.182624</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.521106</v>
+        <v>-0.522026</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.436839</v>
+        <v>-0.436967</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.392714</v>
+        <v>-1.392838</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.05858</v>
+        <v>-0.05876</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.118482</v>
+        <v>0.118299</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.127798</v>
+        <v>-0.128129</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.853567</v>
+        <v>-0.86356</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.269953</v>
+        <v>-1.283909</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.68027</v>
+        <v>-0.740766</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.40591</v>
+        <v>-0.45189</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.046156</v>
+        <v>-1.1303</v>
       </c>
     </row>
     <row r="28">
@@ -2094,52 +2094,52 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.110692</v>
+        <v>-0.111518</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.991412</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.110928</v>
+        <v>-2.138638</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.30896</v>
+        <v>-3.317124</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.170854</v>
+        <v>-0.171256</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.510507</v>
+        <v>-0.511427</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.426578</v>
+        <v>-0.426706</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.382568</v>
+        <v>-1.382692</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.05858</v>
+        <v>-0.05876</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.118482</v>
+        <v>0.118299</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.127798</v>
+        <v>-0.128129</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.853567</v>
+        <v>-0.86356</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.269953</v>
+        <v>-1.283909</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.68027</v>
+        <v>-0.740766</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.40591</v>
+        <v>-0.45189</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.046156</v>
+        <v>-1.1303</v>
       </c>
     </row>
     <row r="30">
@@ -2385,52 +2385,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.004198</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.424623</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.454508</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.007611</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.028827</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.052782</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.052048</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005473</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.009265000000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.01114</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.021759</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.776271</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.782915</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.463855</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.385127</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.177007</v>
       </c>
     </row>
     <row r="35">
@@ -2495,52 +2495,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.004198</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.424623</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.454508</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.007611</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.028827</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.052782</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.052048</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005473</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.009265000000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.01114</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.021759</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.776271</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.782915</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.463855</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.385127</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.177007</v>
       </c>
     </row>
     <row r="37">
@@ -3155,28 +3155,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.007948</v>
+        <v>0.00375</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.448081</v>
+        <v>0.023458</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.479891</v>
+        <v>0.025383</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.017149</v>
+        <v>0.009538</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.028827</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.052782</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.056381</v>
+        <v>0.004333</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.009806</v>
+        <v>0.004333</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -3185,22 +3185,22 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.023437</v>
+        <v>0.001678</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.935124</v>
+        <v>0.158853</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.826958</v>
+        <v>0.044043</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.503635</v>
+        <v>0.03978</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.433446</v>
+        <v>0.048319</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.215518</v>
+        <v>0.038511</v>
       </c>
     </row>
     <row r="49">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
@@ -18614,7 +18614,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -32480,7 +32480,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -36606,7 +36606,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -49254,7 +49254,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E440" s="5" t="n">

--- a/output/pdf_financials_xlsx/TWO.xlsx
+++ b/output/pdf_financials_xlsx/TWO.xlsx
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.019645</v>
+        <v>0.059334</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.09007800000000001</v>
+        <v>0.212389</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.20341</v>
+        <v>0.483557</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.112983</v>
@@ -6147,43 +6147,43 @@
         <v>-0.020869</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.011518</v>
+        <v>0.020184</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.007476</v>
+        <v>0.01336</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>-0.004757</v>
+        <v>-0.006159</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.011464</v>
+        <v>0.008768</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.000976</v>
+        <v>0.007366</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002656</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>0.000741</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.001718</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006833</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>0.005392</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002766</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>0.006681</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>-0.056711</v>
       </c>
     </row>
     <row r="102">
@@ -6422,7 +6422,7 @@
         <v>-0.001241</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.095239</v>
+        <v>0.126941</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>0.156251</v>
@@ -6431,34 +6431,34 @@
         <v>0.060344</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.132019</v>
+        <v>0.129323</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.194644</v>
+        <v>-0.188254</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.031467</v>
+        <v>0.028811</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.004961</v>
+        <v>0.005702</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.006497</v>
+        <v>-0.004779</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.267514</v>
+        <v>-0.274347</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.203032</v>
+        <v>0.208424</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.142604</v>
+        <v>0.139838</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0.169198</v>
+        <v>0.175879</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>-0.011252</v>
+        <v>-0.067963</v>
       </c>
     </row>
     <row r="107">
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.00367</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.006189</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013279</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>-0.002071</v>
@@ -7998,7 +7998,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013279</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>-0.002071</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.693204</v>
+        <v>-0.706483</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-2.186885</v>
@@ -8063,10 +8063,8 @@
       <c r="E135" s="3" t="n">
         <v>-2.638908</v>
       </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F135" s="3" t="n">
+        <v>0.011863</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.287633</v>
@@ -20408,7 +20406,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -24698,7 +24700,11 @@
           <t>(Increase) decrease in GST receivable</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -25084,7 +25090,11 @@
           <t>Net cash generated by (used in) operating activities</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -25932,7 +25942,11 @@
           <t>Decrease in GST receivable</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -26220,7 +26234,11 @@
           <t>Net cash generated by (used in) operating activities</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -26886,7 +26904,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -28826,7 +28848,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -29210,7 +29236,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -46558,7 +46588,11 @@
           <t>Professional and directors fees</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -48478,7 +48512,11 @@
           <t>Professional and directors fees</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E432" s="5" t="n">
         <v>0.039689</v>
       </c>
